--- a/artfynd/A 50582-2025 artfynd.xlsx
+++ b/artfynd/A 50582-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127225076</v>
       </c>
       <c r="B2" t="n">
-        <v>91646</v>
+        <v>91615</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127225066</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>91319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127225129</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127225078</v>
       </c>
       <c r="B5" t="n">
-        <v>97345</v>
+        <v>97314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127225143</v>
+        <v>127225103</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801472</v>
+        <v>801366</v>
       </c>
       <c r="R6" t="n">
-        <v>7404024</v>
+        <v>7404002</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127225103</v>
+        <v>127225143</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801366</v>
+        <v>801472</v>
       </c>
       <c r="R7" t="n">
-        <v>7404002</v>
+        <v>7404024</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127225101</v>
+        <v>127225131</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>801318</v>
+        <v>801287</v>
       </c>
       <c r="R8" t="n">
-        <v>7403907</v>
+        <v>7403879</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127225131</v>
+        <v>127225101</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801287</v>
+        <v>801318</v>
       </c>
       <c r="R9" t="n">
-        <v>7403879</v>
+        <v>7403907</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1454,7 +1454,7 @@
         <v>127225064</v>
       </c>
       <c r="B10" t="n">
-        <v>75153</v>
+        <v>75135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127225089</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>78770</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127225099</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127225133</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127225070</v>
       </c>
       <c r="B14" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>127225135</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>127225072</v>
       </c>
       <c r="B16" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>127225141</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 50582-2025 artfynd.xlsx
+++ b/artfynd/A 50582-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127225076</v>
       </c>
       <c r="B2" t="n">
-        <v>91646</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127225066</v>
+        <v>127735582</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Simonslandet, Lu lm</t>
+          <t>Neitaskaite, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>801301</v>
       </c>
       <c r="R3" t="n">
-        <v>7403992</v>
+        <v>7404002</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +841,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +866,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127225129</v>
+        <v>127415034</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +889,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Simonslandet, Lu lm</t>
+          <t>Neitaskaite, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>801298</v>
+        <v>801419</v>
       </c>
       <c r="R4" t="n">
-        <v>7403883</v>
+        <v>7403889</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -934,12 +947,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,44 +972,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127225078</v>
+        <v>127225066</v>
       </c>
       <c r="B5" t="n">
-        <v>97345</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>801326</v>
+        <v>801301</v>
       </c>
       <c r="R5" t="n">
-        <v>7403833</v>
+        <v>7403992</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,10 +1081,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127225143</v>
+        <v>127735581</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,37 +1092,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Simonslandet, Lu lm</t>
+          <t>Neitaskaite, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801472</v>
+        <v>801300</v>
       </c>
       <c r="R6" t="n">
-        <v>7404024</v>
+        <v>7404002</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1128,12 +1150,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1148,22 +1175,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127225103</v>
+        <v>127225127</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1198,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801366</v>
+        <v>801235</v>
       </c>
       <c r="R7" t="n">
-        <v>7404002</v>
+        <v>7403841</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,10 +1284,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127225101</v>
+        <v>127225129</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1295,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>801318</v>
+        <v>801298</v>
       </c>
       <c r="R8" t="n">
-        <v>7403907</v>
+        <v>7403883</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1357,11 +1384,11 @@
         <v>127225131</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1451,32 +1478,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127225064</v>
+        <v>127225133</v>
       </c>
       <c r="B10" t="n">
-        <v>75153</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1513,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>801471</v>
+        <v>801293</v>
       </c>
       <c r="R10" t="n">
-        <v>7404022</v>
+        <v>7403897</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1548,32 +1575,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127225089</v>
+        <v>127225135</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1610,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801380</v>
+        <v>801317</v>
       </c>
       <c r="R11" t="n">
-        <v>7404098</v>
+        <v>7403912</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1645,10 +1672,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127225099</v>
+        <v>127225137</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1683,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1707,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801296</v>
+        <v>801272</v>
       </c>
       <c r="R12" t="n">
-        <v>7403865</v>
+        <v>7403969</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1742,14 +1769,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127225133</v>
+        <v>127225139</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1777,10 +1804,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801293</v>
+        <v>801268</v>
       </c>
       <c r="R13" t="n">
-        <v>7403897</v>
+        <v>7403961</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1839,32 +1866,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127225070</v>
+        <v>127225141</v>
       </c>
       <c r="B14" t="n">
-        <v>57669</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1901,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801305</v>
+        <v>801294</v>
       </c>
       <c r="R14" t="n">
-        <v>7403988</v>
+        <v>7403990</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1910,11 +1937,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,14 +1963,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127225135</v>
+        <v>127225143</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1976,10 +1998,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>801317</v>
+        <v>801472</v>
       </c>
       <c r="R15" t="n">
-        <v>7403912</v>
+        <v>7404024</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2038,10 +2060,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225072</v>
+        <v>127225063</v>
       </c>
       <c r="B16" t="n">
-        <v>57669</v>
+        <v>83307</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2071,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2095,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801496</v>
+        <v>801270</v>
       </c>
       <c r="R16" t="n">
-        <v>7404005</v>
+        <v>7403961</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2109,11 +2131,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2140,10 +2157,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225141</v>
+        <v>127225064</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>83307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,21 +2168,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2192,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801294</v>
+        <v>801471</v>
       </c>
       <c r="R17" t="n">
-        <v>7403990</v>
+        <v>7404022</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2237,10 +2254,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127735581</v>
+        <v>127415035</v>
       </c>
       <c r="B18" t="n">
-        <v>91452</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,21 +2265,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2276,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>801300</v>
+        <v>801422</v>
       </c>
       <c r="R18" t="n">
-        <v>7404002</v>
+        <v>7403885</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2306,12 +2323,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2343,52 +2360,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127735583</v>
+        <v>127225070</v>
       </c>
       <c r="B19" t="n">
-        <v>98571</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Neitaskaite, Lu lm</t>
+          <t>Simonslandet, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>801371</v>
+        <v>801305</v>
       </c>
       <c r="R19" t="n">
-        <v>7404007</v>
+        <v>7403988</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2412,17 +2425,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2437,64 +2450,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127735579</v>
+        <v>127225072</v>
       </c>
       <c r="B20" t="n">
-        <v>91470</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Neitaskaite, Lu lm</t>
+          <t>Simonslandet, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>801292</v>
+        <v>801496</v>
       </c>
       <c r="R20" t="n">
-        <v>7403857</v>
+        <v>7404005</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2518,17 +2527,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2543,22 +2552,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127735595</v>
+        <v>127225099</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2583,24 +2592,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Neitaskaite, Lu lm</t>
+          <t>Simonslandet, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>801301</v>
+        <v>801296</v>
       </c>
       <c r="R21" t="n">
-        <v>7403875</v>
+        <v>7403865</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2624,17 +2629,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2649,64 +2649,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127735582</v>
+        <v>127225101</v>
       </c>
       <c r="B22" t="n">
-        <v>91748</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Neitaskaite, Lu lm</t>
+          <t>Simonslandet, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>801301</v>
+        <v>801318</v>
       </c>
       <c r="R22" t="n">
-        <v>7404002</v>
+        <v>7403907</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2730,17 +2726,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2755,22 +2746,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127735580</v>
+        <v>127225103</v>
       </c>
       <c r="B23" t="n">
-        <v>98571</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2795,24 +2786,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Neitaskaite, Lu lm</t>
+          <t>Simonslandet, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>801295</v>
+        <v>801366</v>
       </c>
       <c r="R23" t="n">
-        <v>7403864</v>
+        <v>7404002</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2836,17 +2823,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2861,15 +2843,624 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127735580</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Neitaskaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>801295</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7403864</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127735583</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Neitaskaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>801371</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7404007</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127735595</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Neitaskaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>801301</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7403875</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127225078</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Simonslandet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>801326</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7403833</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127225080</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Simonslandet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>801270</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7403961</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127225089</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Simonslandet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>801380</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7404098</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50582-2025 artfynd.xlsx
+++ b/artfynd/A 50582-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225076</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735582</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415034</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225066</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735581</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225127</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1378,6 +1413,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225129</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1475,6 +1515,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225131</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1572,6 +1617,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225133</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1669,6 +1719,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225135</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1766,6 +1821,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225137</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1863,6 +1923,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225139</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1960,6 +2025,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225141</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2057,6 +2127,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225143</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2154,6 +2229,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225063</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2251,6 +2331,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225064</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2357,6 +2442,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415035</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2459,6 +2549,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225070</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2561,6 +2656,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225072</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2658,6 +2758,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225099</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2755,6 +2860,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225101</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2852,6 +2962,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225103</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2958,6 +3073,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735580</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3064,6 +3184,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735583</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3170,6 +3295,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735595</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3267,6 +3397,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225078</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3364,6 +3499,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225080</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3461,8 +3601,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225089</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>